--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.185397411617241</v>
+        <v>0.3551270793878016</v>
       </c>
       <c r="D2" t="n">
-        <v>1.021790576866989</v>
+        <v>0.1660409687408856</v>
       </c>
       <c r="E2" t="n">
-        <v>9.895927752664598</v>
+        <v>1.608088259807997</v>
       </c>
       <c r="F2" t="n">
-        <v>11.01743139652268</v>
+        <v>1.790332601934936</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.47844987740828</v>
+        <v>0.8902481050788454</v>
       </c>
       <c r="D3" t="n">
-        <v>17.78400758196663</v>
+        <v>2.889901232069577</v>
       </c>
       <c r="E3" t="n">
-        <v>9.895927752664598</v>
+        <v>1.608088259807997</v>
       </c>
       <c r="F3" t="n">
-        <v>11.01743139652268</v>
+        <v>1.790332601934936</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.17478987567229</v>
+        <v>4.415903354796747</v>
       </c>
       <c r="D4" t="n">
-        <v>29.44294147028316</v>
+        <v>4.784477988921013</v>
       </c>
       <c r="E4" t="n">
-        <v>9.895927752664598</v>
+        <v>1.608088259807997</v>
       </c>
       <c r="F4" t="n">
-        <v>11.01743139652268</v>
+        <v>1.790332601934936</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.070816324343084</v>
+        <v>0.9865076527057511</v>
       </c>
       <c r="D5" t="n">
-        <v>5.929839050604015</v>
+        <v>0.9635988457231524</v>
       </c>
       <c r="E5" t="n">
-        <v>9.895927752664598</v>
+        <v>1.608088259807997</v>
       </c>
       <c r="F5" t="n">
-        <v>11.01743139652268</v>
+        <v>1.790332601934936</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
